--- a/servers/maze_main_server_dev/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C13057AB-600A-46C5-ABB4-7F2950CF6108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6802F786-8123-483B-9999-0F33800D1B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barires_drop_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_barires_drop_v8!$A$4:$I$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_barires_drop_v8!$A$4:$I$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -39,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -167,35 +165,36 @@
     <t>48300005:1</t>
   </si>
   <si>
+    <t>48200001:2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48200001:3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉技能2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>掉技能3</t>
+  </si>
+  <si>
+    <t>掉技能4</t>
+  </si>
+  <si>
+    <t>掉技能5</t>
+  </si>
+  <si>
+    <t>掉技能6</t>
+  </si>
+  <si>
+    <t>10001,20001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>48300006:1</t>
-  </si>
-  <si>
-    <t>48200001:2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>48200001:3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉血瓶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉技能2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉技能3</t>
-  </si>
-  <si>
-    <t>掉技能4</t>
-  </si>
-  <si>
-    <t>掉技能5</t>
-  </si>
-  <si>
-    <t>掉技能6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -244,11 +243,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -529,7 +527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.625" bestFit="1" customWidth="1"/>
@@ -543,455 +541,547 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
+      <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5">
         <v>11</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5">
         <v>11</v>
       </c>
-      <c r="E5" s="1">
-        <v>10000</v>
-      </c>
-      <c r="F5" s="1">
-        <v>10000</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="E5">
+        <v>10000</v>
+      </c>
+      <c r="F5">
+        <v>10000</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I5" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>38</v>
+      </c>
+      <c r="D6">
+        <v>38</v>
+      </c>
+      <c r="E6">
+        <v>10000</v>
+      </c>
+      <c r="F6">
+        <v>10000</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>56</v>
+      </c>
+      <c r="D7">
+        <v>56</v>
+      </c>
+      <c r="E7">
+        <v>10000</v>
+      </c>
+      <c r="F7">
+        <v>10000</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8">
+        <v>20</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>1000</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>21</v>
+      </c>
+      <c r="D9">
+        <v>25</v>
+      </c>
+      <c r="E9">
+        <v>1001</v>
+      </c>
+      <c r="F9">
+        <v>4000</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>30</v>
+      </c>
+      <c r="D10">
+        <v>30</v>
+      </c>
+      <c r="E10">
+        <v>4001</v>
+      </c>
+      <c r="F10">
+        <v>10000</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>31</v>
+      </c>
+      <c r="D11">
+        <v>31</v>
+      </c>
+      <c r="E11">
+        <v>10000</v>
+      </c>
+      <c r="F11">
+        <v>10000</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>8</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>32</v>
+      </c>
+      <c r="D12">
+        <v>32</v>
+      </c>
+      <c r="E12">
+        <v>10000</v>
+      </c>
+      <c r="F12">
+        <v>10000</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>9</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>33</v>
+      </c>
+      <c r="D13">
+        <v>33</v>
+      </c>
+      <c r="E13">
+        <v>10000</v>
+      </c>
+      <c r="F13">
+        <v>10000</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>10</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14">
+        <v>34</v>
+      </c>
+      <c r="D14">
+        <v>34</v>
+      </c>
+      <c r="E14">
+        <v>10000</v>
+      </c>
+      <c r="F14">
+        <v>10000</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>11</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>35</v>
+      </c>
+      <c r="D15">
+        <v>35</v>
+      </c>
+      <c r="E15">
+        <v>10000</v>
+      </c>
+      <c r="F15">
+        <v>10000</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>10101</v>
+      </c>
+      <c r="B16">
+        <v>101</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="D16">
+        <v>11</v>
+      </c>
+      <c r="E16">
+        <v>10000</v>
+      </c>
+      <c r="F16">
+        <v>10000</v>
+      </c>
+      <c r="H16" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16">
         <v>10001</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1">
-        <v>38</v>
-      </c>
-      <c r="D6" s="1">
-        <v>38</v>
-      </c>
-      <c r="E6" s="1">
-        <v>10000</v>
-      </c>
-      <c r="F6" s="1">
-        <v>10000</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="1" t="s">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>10102</v>
+      </c>
+      <c r="B17">
+        <v>101</v>
+      </c>
+      <c r="C17">
+        <v>13</v>
+      </c>
+      <c r="D17">
+        <v>20</v>
+      </c>
+      <c r="E17">
+        <v>10000</v>
+      </c>
+      <c r="F17">
+        <v>10000</v>
+      </c>
+      <c r="H17" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I17">
         <v>10001</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1">
-        <v>1</v>
-      </c>
-      <c r="C7" s="1">
-        <v>56</v>
-      </c>
-      <c r="D7" s="1">
-        <v>56</v>
-      </c>
-      <c r="E7" s="1">
-        <v>10000</v>
-      </c>
-      <c r="F7" s="1">
-        <v>10000</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="1" t="s">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>10103</v>
+      </c>
+      <c r="B18">
+        <v>101</v>
+      </c>
+      <c r="C18">
+        <v>25</v>
+      </c>
+      <c r="D18">
+        <v>32</v>
+      </c>
+      <c r="E18">
+        <v>10000</v>
+      </c>
+      <c r="F18">
+        <v>10000</v>
+      </c>
+      <c r="H18" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I18">
         <v>10001</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1">
-        <v>2</v>
-      </c>
-      <c r="C8" s="1">
-        <v>20</v>
-      </c>
-      <c r="D8" s="1">
-        <v>20</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="1" t="s">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>10104</v>
+      </c>
+      <c r="B19">
+        <v>101</v>
+      </c>
+      <c r="C19">
         <v>35</v>
       </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1">
-        <v>2</v>
-      </c>
-      <c r="C9" s="1">
-        <v>20</v>
-      </c>
-      <c r="D9" s="1">
-        <v>20</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1001</v>
-      </c>
-      <c r="F9" s="1">
-        <v>4000</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>6</v>
-      </c>
-      <c r="B10" s="1">
-        <v>2</v>
-      </c>
-      <c r="C10" s="1">
-        <v>20</v>
-      </c>
-      <c r="D10" s="1">
-        <v>20</v>
-      </c>
-      <c r="E10" s="1">
-        <v>4001</v>
-      </c>
-      <c r="F10" s="1">
-        <v>10000</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1">
-        <v>3</v>
-      </c>
-      <c r="C11" s="1">
-        <v>20</v>
-      </c>
-      <c r="D11" s="1">
-        <v>20</v>
-      </c>
-      <c r="E11" s="1">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1000</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11" s="1" t="s">
+      <c r="D19">
+        <v>45</v>
+      </c>
+      <c r="E19">
+        <v>10000</v>
+      </c>
+      <c r="F19">
+        <v>10000</v>
+      </c>
+      <c r="H19" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <v>8</v>
-      </c>
-      <c r="B12" s="1">
-        <v>3</v>
-      </c>
-      <c r="C12" s="1">
-        <v>20</v>
-      </c>
-      <c r="D12" s="1">
-        <v>20</v>
-      </c>
-      <c r="E12" s="1">
-        <v>1001</v>
-      </c>
-      <c r="F12" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <v>9</v>
-      </c>
-      <c r="B13" s="1">
-        <v>3</v>
-      </c>
-      <c r="C13" s="1">
-        <v>20</v>
-      </c>
-      <c r="D13" s="1">
-        <v>20</v>
-      </c>
-      <c r="E13" s="1">
-        <v>2001</v>
-      </c>
-      <c r="F13" s="1">
-        <v>3500</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <v>10</v>
-      </c>
-      <c r="B14" s="1">
-        <v>3</v>
-      </c>
-      <c r="C14" s="1">
-        <v>20</v>
-      </c>
-      <c r="D14" s="1">
-        <v>20</v>
-      </c>
-      <c r="E14" s="1">
-        <v>3501</v>
-      </c>
-      <c r="F14" s="1">
-        <v>5000</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
-        <v>11</v>
-      </c>
-      <c r="B15" s="1">
-        <v>3</v>
-      </c>
-      <c r="C15" s="1">
-        <v>20</v>
-      </c>
-      <c r="D15" s="1">
-        <v>20</v>
-      </c>
-      <c r="E15" s="1">
-        <v>5001</v>
-      </c>
-      <c r="F15">
-        <v>7500</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
-        <v>12</v>
-      </c>
-      <c r="B16" s="1">
-        <v>3</v>
-      </c>
-      <c r="C16" s="1">
-        <v>20</v>
-      </c>
-      <c r="D16" s="1">
-        <v>20</v>
-      </c>
-      <c r="E16" s="1">
-        <v>7501</v>
-      </c>
-      <c r="F16">
-        <v>10000</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="I16" s="1">
-        <v>0</v>
+      <c r="I19">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>10105</v>
+      </c>
+      <c r="B20">
+        <v>101</v>
+      </c>
+      <c r="C20">
+        <v>50</v>
+      </c>
+      <c r="D20">
+        <v>70</v>
+      </c>
+      <c r="E20">
+        <v>10000</v>
+      </c>
+      <c r="F20">
+        <v>10000</v>
+      </c>
+      <c r="H20" t="s">
+        <v>28</v>
+      </c>
+      <c r="I20">
+        <v>10001</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I23" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/servers/maze_main_server_dev/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6802F786-8123-483B-9999-0F33800D1B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40DF5E2E-48AF-4B8E-8936-D87BEDB739A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -646,7 +646,7 @@
         <v>11</v>
       </c>
       <c r="E5">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>10000</v>
@@ -675,7 +675,7 @@
         <v>38</v>
       </c>
       <c r="E6">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>10000</v>
@@ -704,7 +704,7 @@
         <v>56</v>
       </c>
       <c r="E7">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>10000</v>
@@ -820,7 +820,7 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>10000</v>
@@ -849,7 +849,7 @@
         <v>32</v>
       </c>
       <c r="E12">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>10000</v>
@@ -878,7 +878,7 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>10000</v>
@@ -907,7 +907,7 @@
         <v>34</v>
       </c>
       <c r="E14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>10000</v>
@@ -936,7 +936,7 @@
         <v>35</v>
       </c>
       <c r="E15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>10000</v>
@@ -965,7 +965,7 @@
         <v>11</v>
       </c>
       <c r="E16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>10000</v>
@@ -991,7 +991,7 @@
         <v>20</v>
       </c>
       <c r="E17">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>10000</v>
@@ -1017,7 +1017,7 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>10000</v>
@@ -1043,7 +1043,7 @@
         <v>45</v>
       </c>
       <c r="E19">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F19">
         <v>10000</v>
@@ -1069,7 +1069,7 @@
         <v>70</v>
       </c>
       <c r="E20">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>10000</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40DF5E2E-48AF-4B8E-8936-D87BEDB739A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D9AB04-1A58-4E3F-8C76-650E02109BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="46">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -194,6 +194,22 @@
   </si>
   <si>
     <t>48300006:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20005</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -962,7 +978,7 @@
         <v>5</v>
       </c>
       <c r="D16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -973,8 +989,8 @@
       <c r="H16" t="s">
         <v>28</v>
       </c>
-      <c r="I16">
-        <v>10001</v>
+      <c r="I16" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
@@ -999,8 +1015,8 @@
       <c r="H17" t="s">
         <v>28</v>
       </c>
-      <c r="I17">
-        <v>10001</v>
+      <c r="I17" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
@@ -1011,7 +1027,7 @@
         <v>101</v>
       </c>
       <c r="C18">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D18">
         <v>32</v>
@@ -1025,8 +1041,8 @@
       <c r="H18" t="s">
         <v>28</v>
       </c>
-      <c r="I18">
-        <v>10001</v>
+      <c r="I18" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
@@ -1037,7 +1053,7 @@
         <v>101</v>
       </c>
       <c r="C19">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D19">
         <v>45</v>
@@ -1051,8 +1067,8 @@
       <c r="H19" t="s">
         <v>28</v>
       </c>
-      <c r="I19">
-        <v>10001</v>
+      <c r="I19" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
@@ -1063,10 +1079,10 @@
         <v>101</v>
       </c>
       <c r="C20">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D20">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1077,8 +1093,8 @@
       <c r="H20" t="s">
         <v>28</v>
       </c>
-      <c r="I20">
-        <v>10001</v>
+      <c r="I20" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server_dev/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D9AB04-1A58-4E3F-8C76-650E02109BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CC5893-FD17-41D4-8BA4-B359564E7825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="47">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -197,19 +197,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10001,20002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001,20005</t>
+    <t>10001,20001,30001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20002,30001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20003,30001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20004,30001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20005,30001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -990,7 +994,7 @@
         <v>28</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
@@ -1016,7 +1020,7 @@
         <v>28</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
@@ -1042,7 +1046,7 @@
         <v>28</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
@@ -1068,7 +1072,7 @@
         <v>28</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
@@ -1094,7 +1098,7 @@
         <v>28</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server_dev/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16CC5893-FD17-41D4-8BA4-B359564E7825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1245DE50-4840-48C4-B670-2CE25BCF9A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -214,6 +214,18 @@
   </si>
   <si>
     <t>10001,20005,30001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20006,30001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20007,30001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20008,30001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -547,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.625" bestFit="1" customWidth="1"/>
@@ -1101,6 +1113,84 @@
         <v>46</v>
       </c>
     </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>10106</v>
+      </c>
+      <c r="B21">
+        <v>101</v>
+      </c>
+      <c r="C21">
+        <v>79</v>
+      </c>
+      <c r="D21">
+        <v>350</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>10000</v>
+      </c>
+      <c r="H21" t="s">
+        <v>28</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>10107</v>
+      </c>
+      <c r="B22">
+        <v>101</v>
+      </c>
+      <c r="C22">
+        <v>351</v>
+      </c>
+      <c r="D22">
+        <v>700</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>10000</v>
+      </c>
+      <c r="H22" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>10108</v>
+      </c>
+      <c r="B23">
+        <v>101</v>
+      </c>
+      <c r="C23">
+        <v>701</v>
+      </c>
+      <c r="D23">
+        <v>1100</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>10000</v>
+      </c>
+      <c r="H23" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server_dev/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_barires_drop_v8【迷宫-关卡-掉落物品】.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1245DE50-4840-48C4-B670-2CE25BCF9A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="29100" windowHeight="14540"/>
   </bookViews>
   <sheets>
     <sheet name="maze_barires_drop_v8" sheetId="1" r:id="rId1"/>
@@ -20,9 +14,6 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -30,6 +21,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,219 +30,346 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="58">
   <si>
     <t>paipaiworld_config</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>INT_K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_C</t>
+  </si>
+  <si>
+    <t>STRING</t>
+  </si>
+  <si>
+    <t>MAP&lt;INT:LONG&gt;_C</t>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_C</t>
   </si>
   <si>
     <t>order</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop_id</t>
+  </si>
+  <si>
+    <t>in_barries_kill_min</t>
+  </si>
+  <si>
+    <t>in_barries_kill_max</t>
+  </si>
+  <si>
+    <t>drop_ratio_min</t>
+  </si>
+  <si>
+    <t>drop_ratio_max</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>drop_items</t>
+  </si>
+  <si>
+    <t>drop_condition</t>
   </si>
   <si>
     <t>序号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>掉落id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>杀怪数小</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>杀怪数大</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>掉落几率万分比</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
   </si>
   <si>
     <t>掉落物品：数量</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>掉落条件id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STRING</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>in_barries_kill_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>in_barries_kill_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_items</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_condition</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAP&lt;INT:LONG&gt;_C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_ratio_min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_ratio_max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>drop_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>desc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LIST&lt;INT&gt;_C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>30%血掉血瓶</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48300001:1</t>
+  </si>
+  <si>
+    <t>10001,20001</t>
   </si>
   <si>
     <t>掉3个三选一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48200001:3</t>
   </si>
   <si>
     <t>掉2个三选一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48200001:2</t>
   </si>
   <si>
     <t>掉1个三选一</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>48200001:1</t>
   </si>
   <si>
-    <t>48300001:1</t>
+    <t>掉技能2</t>
   </si>
   <si>
     <t>48300002:1</t>
   </si>
   <si>
+    <t>掉技能3</t>
+  </si>
+  <si>
     <t>48300003:1</t>
   </si>
   <si>
+    <t>掉技能4</t>
+  </si>
+  <si>
     <t>48300004:1</t>
   </si>
   <si>
+    <t>掉技能5</t>
+  </si>
+  <si>
     <t>48300005:1</t>
   </si>
   <si>
-    <t>48200001:2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>48200001:3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉技能2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>掉技能3</t>
-  </si>
-  <si>
-    <t>掉技能4</t>
-  </si>
-  <si>
-    <t>掉技能5</t>
-  </si>
-  <si>
     <t>掉技能6</t>
   </si>
   <si>
-    <t>10001,20001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>48300006:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20001,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20002,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20003,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20004,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20005,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20006,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20007,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10001,20008,30001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10001,20009,30001</t>
+  </si>
+  <si>
+    <t>10001,20010,30001</t>
+  </si>
+  <si>
+    <t>10001,20011,30001</t>
+  </si>
+  <si>
+    <t>30001,20001,40001</t>
+  </si>
+  <si>
+    <t>30001,20002,40001</t>
+  </si>
+  <si>
+    <t>30001,20003,40001</t>
+  </si>
+  <si>
+    <t>30001,20004,40001</t>
+  </si>
+  <si>
+    <t>30001,20005,40001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
-      <family val="3"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -258,12 +378,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.149998474074526"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -271,26 +577,313 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -339,7 +932,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -374,7 +967,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -548,123 +1141,118 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.625" customWidth="1"/>
+    <col min="2" max="2" width="8.75" customWidth="1"/>
+    <col min="3" max="3" width="16.25" customWidth="1"/>
+    <col min="4" max="4" width="16.75" customWidth="1"/>
+    <col min="5" max="6" width="17.125" customWidth="1"/>
+    <col min="7" max="7" width="12.25" customWidth="1"/>
+    <col min="8" max="8" width="18.75" customWidth="1"/>
+    <col min="9" max="9" width="19.5714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="G3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>1</v>
       </c>
@@ -687,13 +1275,13 @@
         <v>23</v>
       </c>
       <c r="H5" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>2</v>
       </c>
@@ -716,13 +1304,13 @@
         <v>23</v>
       </c>
       <c r="H6" t="s">
-        <v>28</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>3</v>
       </c>
@@ -745,13 +1333,13 @@
         <v>23</v>
       </c>
       <c r="H7" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>4</v>
       </c>
@@ -771,16 +1359,16 @@
         <v>1000</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H8" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>5</v>
       </c>
@@ -800,16 +1388,16 @@
         <v>4000</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H9" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>6</v>
       </c>
@@ -829,16 +1417,16 @@
         <v>10000</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>7</v>
       </c>
@@ -858,16 +1446,16 @@
         <v>10000</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>8</v>
       </c>
@@ -887,16 +1475,16 @@
         <v>10000</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H12" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>9</v>
       </c>
@@ -916,16 +1504,16 @@
         <v>10000</v>
       </c>
       <c r="G13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" t="s">
         <v>37</v>
       </c>
-      <c r="H13" t="s">
-        <v>31</v>
-      </c>
       <c r="I13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9">
       <c r="A14">
         <v>10</v>
       </c>
@@ -948,13 +1536,13 @@
         <v>38</v>
       </c>
       <c r="H14" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9">
       <c r="A15">
         <v>11</v>
       </c>
@@ -974,7 +1562,7 @@
         <v>10000</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H15" t="s">
         <v>41</v>
@@ -983,7 +1571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9">
       <c r="A16">
         <v>10101</v>
       </c>
@@ -994,7 +1582,7 @@
         <v>5</v>
       </c>
       <c r="D16">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1003,13 +1591,13 @@
         <v>10000</v>
       </c>
       <c r="H16" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9">
       <c r="A17">
         <v>10102</v>
       </c>
@@ -1017,10 +1605,10 @@
         <v>101</v>
       </c>
       <c r="C17">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D17">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1029,13 +1617,13 @@
         <v>10000</v>
       </c>
       <c r="H17" t="s">
-        <v>28</v>
-      </c>
-      <c r="I17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9">
       <c r="A18">
         <v>10103</v>
       </c>
@@ -1043,10 +1631,10 @@
         <v>101</v>
       </c>
       <c r="C18">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D18">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1055,13 +1643,13 @@
         <v>10000</v>
       </c>
       <c r="H18" t="s">
-        <v>28</v>
-      </c>
-      <c r="I18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9">
       <c r="A19">
         <v>10104</v>
       </c>
@@ -1069,25 +1657,25 @@
         <v>101</v>
       </c>
       <c r="C19">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D19">
+        <v>50</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>10000</v>
+      </c>
+      <c r="H19" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>10000</v>
-      </c>
-      <c r="H19" t="s">
-        <v>28</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20">
         <v>10105</v>
       </c>
@@ -1095,25 +1683,25 @@
         <v>101</v>
       </c>
       <c r="C20">
+        <v>51</v>
+      </c>
+      <c r="D20">
+        <v>65</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>10000</v>
+      </c>
+      <c r="H20" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D20">
-        <v>72</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>10000</v>
-      </c>
-      <c r="H20" t="s">
-        <v>28</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21">
         <v>10106</v>
       </c>
@@ -1121,10 +1709,10 @@
         <v>101</v>
       </c>
       <c r="C21">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D21">
-        <v>350</v>
+        <v>81</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1133,13 +1721,13 @@
         <v>10000</v>
       </c>
       <c r="H21" t="s">
-        <v>28</v>
-      </c>
-      <c r="I21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9">
       <c r="A22">
         <v>10107</v>
       </c>
@@ -1147,10 +1735,10 @@
         <v>101</v>
       </c>
       <c r="C22">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="D22">
-        <v>700</v>
+        <v>97</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1159,13 +1747,13 @@
         <v>10000</v>
       </c>
       <c r="H22" t="s">
-        <v>28</v>
-      </c>
-      <c r="I22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9">
       <c r="A23">
         <v>10108</v>
       </c>
@@ -1173,10 +1761,10 @@
         <v>101</v>
       </c>
       <c r="C23">
-        <v>701</v>
+        <v>98</v>
       </c>
       <c r="D23">
-        <v>1100</v>
+        <v>114</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1185,14 +1773,231 @@
         <v>10000</v>
       </c>
       <c r="H23" t="s">
-        <v>28</v>
-      </c>
-      <c r="I23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>49</v>
       </c>
     </row>
+    <row r="24" spans="1:9">
+      <c r="A24">
+        <v>10109</v>
+      </c>
+      <c r="B24">
+        <v>101</v>
+      </c>
+      <c r="C24">
+        <v>115</v>
+      </c>
+      <c r="D24">
+        <v>132</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>10000</v>
+      </c>
+      <c r="H24" t="s">
+        <v>24</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25">
+        <v>10110</v>
+      </c>
+      <c r="B25">
+        <v>101</v>
+      </c>
+      <c r="C25">
+        <v>133</v>
+      </c>
+      <c r="D25">
+        <v>151</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>10000</v>
+      </c>
+      <c r="H25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26">
+        <v>10111</v>
+      </c>
+      <c r="B26">
+        <v>101</v>
+      </c>
+      <c r="C26">
+        <v>152</v>
+      </c>
+      <c r="D26">
+        <v>172</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>10000</v>
+      </c>
+      <c r="H26" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27">
+        <v>10112</v>
+      </c>
+      <c r="B27">
+        <v>201</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>10000</v>
+      </c>
+      <c r="H27" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28">
+        <v>10113</v>
+      </c>
+      <c r="B28">
+        <v>201</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+      <c r="D28">
+        <v>5</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>10000</v>
+      </c>
+      <c r="H28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29">
+        <v>10114</v>
+      </c>
+      <c r="B29">
+        <v>201</v>
+      </c>
+      <c r="C29">
+        <v>6</v>
+      </c>
+      <c r="D29">
+        <v>8</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>10000</v>
+      </c>
+      <c r="H29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30">
+        <v>10115</v>
+      </c>
+      <c r="B30">
+        <v>201</v>
+      </c>
+      <c r="C30">
+        <v>9</v>
+      </c>
+      <c r="D30">
+        <v>11</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>10000</v>
+      </c>
+      <c r="H30" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31">
+        <v>10116</v>
+      </c>
+      <c r="B31">
+        <v>201</v>
+      </c>
+      <c r="C31">
+        <v>12</v>
+      </c>
+      <c r="D31">
+        <v>99</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>10000</v>
+      </c>
+      <c r="H31" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="9:9">
+      <c r="I32" s="2"/>
+    </row>
+    <row r="33" spans="9:9">
+      <c r="I33" s="2"/>
+    </row>
+    <row r="34" spans="9:9">
+      <c r="I34" s="2"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>